--- a/docs/venue-model-andover-unit-28.xlsx
+++ b/docs/venue-model-andover-unit-28.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 year" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capital" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Momentum Ltd" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -579,14 +580,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Netball courts</t>
+          <t>Netball courts (one per 20 m span; a 4th fits the east block at league run-offs, in place of padel)</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>4</v>
@@ -597,21 +598,21 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4 courts + 4 padel + gym fits 4,047 sq m on paper. Survey first.</t>
+          <t>Hollis survey: column rows at 20 m, frames at 7.5 m</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Padel courts</t>
+          <t>Padel courts (21 m spans only: 3 in the east block, 2 south of Court 3)</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
         <v>4</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>5</v>
@@ -622,78 +623,120 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LTA: 6 m sides, 8 m at ridge. 7.1 m eaves should pass.</t>
+          <t>LTA: 6 m sides, 8 m at ridge. Needs the 75 m line clear.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Operating weeks per year</t>
+          <t>Pickleball courts (span B end, 18 m x 20 m takes 2)</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E9" s="8">
         <f>CHOOSE($C$2,B9,C9,D9)</f>
         <v/>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>18.3 x 9.1 m each, 5.5 m height. Cheap to mark, fast-growing daytime demand</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Physio / clinic rooms (in the offices)</t>
+          <t>Winter cricket net lanes over netball courts (retractable, 4 per court)</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E10" s="8">
         <f>CHOOSE($C$2,B10,C10,D10)</f>
         <v/>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jan to Apr daytime dual use. 0 to switch off</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bouldering room, sq m (option: replaces the 2 padel courts south of Court 3, ~460 sq m)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <f>CHOOSE($C$2,B11,C11,D11)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Set padel to 3 if you use this. 4.5 m walls fit under 7.1 m eaves</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Netball — external hire (clubs, ADNA, Hampshire, schools). Momentum's own use is excluded below</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Operating weeks per year</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" s="8">
+        <f>CHOOSE($C$2,B12,C12,D12)</f>
+        <v/>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Evening court-hours per court per week (18:00–22:00 x 5)</t>
+          <t>Physio / clinic rooms (in the offices)</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E13" s="8">
         <f>CHOOSE($C$2,B13,C13,D13)</f>
@@ -701,68 +744,34 @@
       </c>
       <c r="F13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Court-hours per week Momentum uses in the evening</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="E14" s="8">
-        <f>CHOOSE($C$2,B14,C14,D14)</f>
-        <v/>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>40 matches x 40 min today = ~27</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Evening fill of the remaining hours</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E15" s="10">
-        <f>CHOOSE($C$2,B15,C15,D15)</f>
-        <v/>
-      </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Netball — external hire (clubs, ADNA, Hampshire, schools). Momentum's own use is excluded below</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Evening rate per court-hour</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="C16" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="E16" s="12">
+          <t>Evening court-hours per court per week (18:00–22:00 x 5)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" s="8">
         <f>CHOOSE($C$2,B16,C16,D16)</f>
         <v/>
       </c>
@@ -771,38 +780,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Weekend court-hours per court per week (10 x 2)</t>
+          <t>Court-hours per week Momentum uses in the evening</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E17" s="8">
         <f>CHOOSE($C$2,B17,C17,D17)</f>
         <v/>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>40 matches x 40 min today = ~27</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Weekend fill</t>
+          <t>Evening fill of the remaining hours</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.55</v>
+        <v>0.8</v>
       </c>
       <c r="E18" s="10">
         <f>CHOOSE($C$2,B18,C18,D18)</f>
@@ -813,17 +826,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Weekend rate per court-hour</t>
+          <t>Evening rate per court-hour</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E19" s="12">
         <f>CHOOSE($C$2,B19,C19,D19)</f>
@@ -834,17 +847,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Weekday daytime court-hours per court per week (8 x 5)</t>
+          <t>Weekend court-hours per court per week (10 x 2)</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E20" s="8">
         <f>CHOOSE($C$2,B20,C20,D20)</f>
@@ -855,17 +868,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Daytime fill (schools, walking netball, Mini Momentum)</t>
+          <t>Weekend fill</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.28</v>
+        <v>0.55</v>
       </c>
       <c r="E21" s="10">
         <f>CHOOSE($C$2,B21,C21,D21)</f>
@@ -876,17 +889,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daytime rate per court-hour</t>
+          <t>Weekend rate per court-hour</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E22" s="12">
         <f>CHOOSE($C$2,B22,C22,D22)</f>
@@ -894,140 +907,170 @@
       </c>
       <c r="F22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Weekday daytime court-hours per court per week (8 x 5)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E23" s="8">
+        <f>CHOOSE($C$2,B23,C23,D23)</f>
+        <v/>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Momentum programmes moved in-house (leagues, mixed, pay to play, Netball Hour, walking, coaching)</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Daytime fill (schools, walking netball, Mini Momentum)</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E24" s="10">
+        <f>CHOOSE($C$2,B24,C24,D24)</f>
+        <v/>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Momentum model: 1 = CIC runs the programmes, 2 = Momentum Netball Ltd rents courts from the CIC</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="8">
+          <t>Daytime rate per court-hour</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E25" s="12">
         <f>CHOOSE($C$2,B25,C25,D25)</f>
         <v/>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Mode 2 keeps Momentum Ltd independent; the CIC must charge it an arm's-length rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Mode 1: steady-state programme income inside the CIC</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n">
-        <v>90000</v>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>120000</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="E26" s="12">
-        <f>CHOOSE($C$2,B26,C26,D26)</f>
-        <v/>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Xero FY26: £55k across all programmes on ~20 court-hours/week</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Mode 2: block-booking discount available to any block booker</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E27" s="10">
-        <f>CHOOSE($C$2,B27,C27,D27)</f>
-        <v/>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Same 15% as the 2025 sheet; must be offered to all, not just Momentum</t>
-        </is>
-      </c>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Momentum programmes moved in-house (leagues, mixed, pay to play, Netball Hour, walking, coaching)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mode 2: weeks per year Momentum books</t>
+          <t>Momentum model: 1 = CIC runs the programmes, 2 = Momentum Netball Ltd rents courts from the CIC</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E28" s="8">
         <f>CHOOSE($C$2,B28,C28,D28)</f>
         <v/>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mode 2 keeps Momentum Ltd independent; the CIC must charge it an arm's-length rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mode 1: steady-state programme income inside the CIC</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="E29" s="12">
+        <f>CHOOSE($C$2,B29,C29,D29)</f>
+        <v/>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Xero FY26: £55k across all programmes on ~20 court-hours/week</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Padel</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mode 2: block-booking discount available to any block booker</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E30" s="10">
+        <f>CHOOSE($C$2,B30,C30,D30)</f>
+        <v/>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Same 15% as the 2025 sheet; must be offered to all, not just Momentum</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hours open per court per week (07:00–22:00 x 7)</t>
+          <t>Mode 2: weeks per year Momentum books</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="E31" s="8">
         <f>CHOOSE($C$2,B31,C31,D31)</f>
@@ -1035,149 +1078,111 @@
       </c>
       <c r="F31" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Padel</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Hours open per court per week (07:00–22:00 x 7)</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="E34" s="8">
+        <f>CHOOSE($C$2,B34,C34,D34)</f>
+        <v/>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Blended fill</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B35" s="9" t="n">
         <v>0.35</v>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C35" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D35" s="9" t="n">
         <v>0.55</v>
       </c>
-      <c r="E32" s="10">
-        <f>CHOOSE($C$2,B32,C32,D32)</f>
-        <v/>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="E35" s="10">
+        <f>CHOOSE($C$2,B35,C35,D35)</f>
+        <v/>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>UK indoor padel typically 50–65% by year 2</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Blended rate per court-hour</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="E33" s="12">
-        <f>CHOOSE($C$2,B33,C33,D33)</f>
-        <v/>
-      </c>
-      <c r="F33" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Gym and netball strength &amp; conditioning</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gym members (steady state)</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n">
-        <v>300</v>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>450</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>650</v>
-      </c>
-      <c r="E36" s="8">
+          <t>Blended rate per court-hour</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E36" s="12">
         <f>CHOOSE($C$2,B36,C36,D36)</f>
         <v/>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>PureGym Andover from £22.99; this is a niche, coached, women-led offer</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Monthly fee</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="C37" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="D37" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="E37" s="12">
-        <f>CHOOSE($C$2,B37,C37,D37)</f>
-        <v/>
-      </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>S&amp;C / injury-prevention classes per week</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="E38" s="8">
-        <f>CHOOSE($C$2,B38,C38,D38)</f>
-        <v/>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>ACL prevention is netball's biggest unmet need; 7% of players do a programme</t>
-        </is>
-      </c>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Pickleball</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Attendees per class</t>
+          <t>Hours open per court per week (12 x 7)</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E39" s="8">
         <f>CHOOSE($C$2,B39,C39,D39)</f>
@@ -1188,252 +1193,256 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Price per attendee</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E40" s="12">
+          <t>Blended fill</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E40" s="10">
         <f>CHOOSE($C$2,B40,C40,D40)</f>
         <v/>
       </c>
       <c r="F40" t="inlineStr"/>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Physio and clinic</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Rate per court-hour</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="E41" s="12">
+        <f>CHOOSE($C$2,B41,C41,D41)</f>
+        <v/>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Room rent per room per month</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>900</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E43" s="12">
-        <f>CHOOSE($C$2,B43,C43,D43)</f>
-        <v/>
-      </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Winter cricket nets (dual use of netball courts, weekday daytime)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Injury-prevention programmes sold to clubs and schools</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E44" s="12">
+          <t>Weeks per year (January to April)</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E44" s="8">
         <f>CHOOSE($C$2,B44,C44,D44)</f>
         <v/>
       </c>
       <c r="F44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Lane-hours per lane per week (6 h x 5 days)</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E45" s="8">
+        <f>CHOOSE($C$2,B45,C45,D45)</f>
+        <v/>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Café and bar</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Fill</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E46" s="10">
+        <f>CHOOSE($C$2,B46,C46,D46)</f>
+        <v/>
+      </c>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Visits per week (all activities)</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>5200</v>
-      </c>
-      <c r="E47" s="8">
+          <t>Rate per lane-hour</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="E47" s="12">
         <f>CHOOSE($C$2,B47,C47,D47)</f>
         <v/>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>4 netball courts x 20 people per court-hour evening + padel + gym + daytime</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Average spend per visit</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C48" s="13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D48" s="13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E48" s="14">
-        <f>CHOOSE($C$2,B48,C48,D48)</f>
-        <v/>
-      </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Café gross margin</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C49" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D49" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E49" s="10">
-        <f>CHOOSE($C$2,B49,C49,D49)</f>
-        <v/>
-      </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Bouldering room (option)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Income per sq m per year</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>900</v>
+      </c>
+      <c r="E50" s="12">
+        <f>CHOOSE($C$2,B50,C50,D50)</f>
+        <v/>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>UK bouldering gyms run £600 to £900 per sq m; entry ~£11</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Events, camps, parties, rooms</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Tournaments and events per year</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="E52" s="8">
-        <f>CHOOSE($C$2,B52,C52,D52)</f>
-        <v/>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>County finals, Momentum tournaments, Army championships, EN courses</t>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Extra staff cost if the room exists</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>52000</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>52000</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E51" s="12">
+        <f>CHOOSE($C$2,B51,C51,D51)</f>
+        <v/>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2 x £26k route setters / floor staff</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Net income per event</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D53" s="11" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E53" s="12">
-        <f>CHOOSE($C$2,B53,C53,D53)</f>
-        <v/>
-      </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Gym and netball strength &amp; conditioning</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Holiday camp weeks</t>
+          <t>Gym members (steady state)</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>12</v>
+        <v>450</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>13</v>
+        <v>650</v>
       </c>
       <c r="E54" s="8">
         <f>CHOOSE($C$2,B54,C54,D54)</f>
         <v/>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PureGym Andover from £22.99; this is a niche, coached, women-led offer</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kids per day</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="E55" s="8">
+          <t>Monthly fee</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E55" s="12">
         <f>CHOOSE($C$2,B55,C55,D55)</f>
         <v/>
       </c>
@@ -1442,40 +1451,44 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Price per kid per day</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="C56" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="D56" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="E56" s="12">
+          <t>S&amp;C / injury-prevention classes per week</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E56" s="8">
         <f>CHOOSE($C$2,B56,C56,D56)</f>
         <v/>
       </c>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ACL prevention is netball's biggest unmet need; 7% of players do a programme</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Parties per week</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C57" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D57" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" s="16">
+          <t>Attendees per class</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" s="8">
         <f>CHOOSE($C$2,B57,C57,D57)</f>
         <v/>
       </c>
@@ -1484,17 +1497,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Price per party</t>
+          <t>Price per attendee</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
-        <v>220</v>
+        <v>7</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>250</v>
+        <v>8</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>280</v>
+        <v>9</v>
       </c>
       <c r="E58" s="12">
         <f>CHOOSE($C$2,B58,C58,D58)</f>
@@ -1502,203 +1515,165 @@
       </c>
       <c r="F58" t="inlineStr"/>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Meeting room hire per year</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C59" s="11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D59" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E59" s="12">
-        <f>CHOOSE($C$2,B59,C59,D59)</f>
-        <v/>
-      </c>
-      <c r="F59" t="inlineStr"/>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Physio and clinic</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Sponsorship and donations</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Room rent per room per month</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>900</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E61" s="12">
+        <f>CHOOSE($C$2,B61,C61,D61)</f>
+        <v/>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Venue naming rights</t>
+          <t>Injury-prevention programmes sold to clubs and schools</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D62" s="11" t="n">
         <v>20000</v>
-      </c>
-      <c r="C62" s="11" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D62" s="11" t="n">
-        <v>50000</v>
       </c>
       <c r="E62" s="12">
         <f>CHOOSE($C$2,B62,C62,D62)</f>
         <v/>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Simplyhealth, Le Creuset, Stannah, Twinings, Lloyds, Ocado all in Andover</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Court sponsors (count)</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C63" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D63" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E63" s="8">
-        <f>CHOOSE($C$2,B63,C63,D63)</f>
-        <v/>
-      </c>
-      <c r="F63" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Fee per court sponsor</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C64" s="11" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D64" s="11" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E64" s="12">
-        <f>CHOOSE($C$2,B64,C64,D64)</f>
-        <v/>
-      </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Café and bar</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Other sponsorship</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C65" s="11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D65" s="11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E65" s="12">
+          <t>Visits per week (all activities)</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E65" s="8">
         <f>CHOOSE($C$2,B65,C65,D65)</f>
         <v/>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>4 netball courts x 20 people per court-hour evening + padel + gym + daytime</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Donations and fundraising</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D66" s="11" t="n">
-        <v>35000</v>
-      </c>
-      <c r="E66" s="12">
+          <t>Average spend per visit</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E66" s="14">
         <f>CHOOSE($C$2,B66,C66,D66)</f>
         <v/>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Gift Aid adds 25% only for a charity or CASC</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Occupancy costs</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Café gross margin</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E67" s="10">
+        <f>CHOOSE($C$2,B67,C67,D67)</f>
+        <v/>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C69" s="11" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D69" s="11" t="n">
-        <v>450000</v>
-      </c>
-      <c r="E69" s="12">
-        <f>CHOOSE($C$2,B69,C69,D69)</f>
-        <v/>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>£9.57 per sq ft, FRI</t>
-        </is>
-      </c>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Events, camps, parties, rooms</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Rent-free months in year 1</t>
+          <t>Tournaments and events per year</t>
         </is>
       </c>
       <c r="B70" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E70" s="8">
         <f>CHOOSE($C$2,B70,C70,D70)</f>
@@ -1706,26 +1681,26 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Unit empty since 2023; landlord's empty-rates relief ends ~Sept 2026</t>
+          <t>County finals, Momentum tournaments, Army championships, EN courses</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Year 2 rent as % of headline</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D71" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E71" s="10">
+          <t>Net income per event</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E71" s="12">
         <f>CHOOSE($C$2,B71,C71,D71)</f>
         <v/>
       </c>
@@ -1734,44 +1709,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Rateable value</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C72" s="11" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D72" s="11" t="n">
-        <v>400000</v>
-      </c>
-      <c r="E72" s="12">
+          <t>Holiday camp weeks</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E72" s="8">
         <f>CHOOSE($C$2,B72,C72,D72)</f>
         <v/>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>VOA 2026 list. A sports-use revaluation may lower it.</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Rates multiplier 2026/27</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="C73" s="17" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="D73" s="17" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E73" s="18">
+          <t>Kids per day</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E73" s="8">
         <f>CHOOSE($C$2,B73,C73,D73)</f>
         <v/>
       </c>
@@ -1780,35 +1751,40 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Rates relief % override (blank = use structure)</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="9" t="n"/>
-      <c r="E74" s="19" t="n"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>TVBC can grant a local non-profit up to 100% at its discretion</t>
-        </is>
-      </c>
+          <t>Price per kid per day</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="E74" s="12">
+        <f>CHOOSE($C$2,B74,C74,D74)</f>
+        <v/>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C75" s="11" t="n">
-        <v>18000</v>
-      </c>
-      <c r="D75" s="11" t="n">
-        <v>16000</v>
-      </c>
-      <c r="E75" s="12">
+          <t>Parties per week</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C75" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" s="16">
         <f>CHOOSE($C$2,B75,C75,D75)</f>
         <v/>
       </c>
@@ -1817,17 +1793,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Repairs and maintenance sinking fund (FRI)</t>
+          <t>Price per party</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
-        <v>45000</v>
+        <v>220</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>40000</v>
+        <v>250</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>35000</v>
+        <v>280</v>
       </c>
       <c r="E76" s="12">
         <f>CHOOSE($C$2,B76,C76,D76)</f>
@@ -1838,17 +1814,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Utilities gross</t>
+          <t>Meeting room hire per year</t>
         </is>
       </c>
       <c r="B77" s="11" t="n">
-        <v>90000</v>
+        <v>8000</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>80000</v>
+        <v>15000</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>70000</v>
+        <v>22000</v>
       </c>
       <c r="E77" s="12">
         <f>CHOOSE($C$2,B77,C77,D77)</f>
@@ -1856,55 +1832,59 @@
       </c>
       <c r="F77" t="inlineStr"/>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Benefit of the 438 kWp roof PV (if the tenant gets the power)</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C78" s="11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D78" s="11" t="n">
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Sponsorship and donations</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Venue naming rights</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D80" s="11" t="n">
         <v>50000</v>
       </c>
-      <c r="E78" s="12">
-        <f>CHOOSE($C$2,B78,C78,D78)</f>
-        <v/>
-      </c>
-      <c r="F78" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Staff (salaries; on-costs added below)</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="6" t="n"/>
-      <c r="D80" s="6" t="n"/>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="6" t="n"/>
+      <c r="E80" s="12">
+        <f>CHOOSE($C$2,B80,C80,D80)</f>
+        <v/>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Simplyhealth, Le Creuset, Stannah, Twinings, Lloyds, Ocado all in Andover</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>General manager</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="n">
-        <v>45000</v>
-      </c>
-      <c r="C81" s="11" t="n">
-        <v>45000</v>
-      </c>
-      <c r="D81" s="11" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E81" s="12">
+          <t>Court sponsors (count)</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E81" s="8">
         <f>CHOOSE($C$2,B81,C81,D81)</f>
         <v/>
       </c>
@@ -1913,19 +1893,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Duty managers (count)</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C82" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D82" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E82" s="8">
+          <t>Fee per court sponsor</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E82" s="12">
         <f>CHOOSE($C$2,B82,C82,D82)</f>
         <v/>
       </c>
@@ -1934,17 +1914,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Duty manager salary</t>
+          <t>Other sponsorship</t>
         </is>
       </c>
       <c r="B83" s="11" t="n">
-        <v>28000</v>
+        <v>5000</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>28000</v>
+        <v>15000</v>
       </c>
       <c r="E83" s="12">
         <f>CHOOSE($C$2,B83,C83,D83)</f>
@@ -1955,122 +1935,104 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Reception and café staff (FTE)</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C84" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D84" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E84" s="8">
+          <t>Donations and fundraising</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C84" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D84" s="11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E84" s="12">
         <f>CHOOSE($C$2,B84,C84,D84)</f>
         <v/>
       </c>
-      <c r="F84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Reception / café salary</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="n">
-        <v>24000</v>
-      </c>
-      <c r="C85" s="11" t="n">
-        <v>24000</v>
-      </c>
-      <c r="D85" s="11" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E85" s="12">
-        <f>CHOOSE($C$2,B85,C85,D85)</f>
-        <v/>
-      </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Gift Aid adds 25% only for a charity or CASC</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Cleaners (FTE)</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C86" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E86" s="8">
-        <f>CHOOSE($C$2,B86,C86,D86)</f>
-        <v/>
-      </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy costs</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n"/>
+      <c r="F86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cleaner salary</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="B87" s="11" t="n">
-        <v>22000</v>
+        <v>450000</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>22000</v>
+        <v>450000</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>22000</v>
+        <v>450000</v>
       </c>
       <c r="E87" s="12">
         <f>CHOOSE($C$2,B87,C87,D87)</f>
         <v/>
       </c>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>£9.57 per sq ft, FRI</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Marketing and community officer</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C88" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D88" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E88" s="12">
+          <t>Rent-free months in year 1</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="E88" s="8">
         <f>CHOOSE($C$2,B88,C88,D88)</f>
         <v/>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Unit empty since 2023; landlord's empty-rates relief ends ~Sept 2026</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Coaching cost as % of Momentum programme + S&amp;C income</t>
+          <t>Year 2 rent as % of headline</t>
         </is>
       </c>
       <c r="B89" s="9" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="C89" s="9" t="n">
-        <v>0.35</v>
+        <v>0.85</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
       <c r="E89" s="10">
         <f>CHOOSE($C$2,B89,C89,D89)</f>
@@ -2081,80 +2043,102 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Employer on-costs (NI, pension)</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C90" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D90" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E90" s="10">
+          <t>Rateable value</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C90" s="11" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D90" s="11" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E90" s="12">
         <f>CHOOSE($C$2,B90,C90,D90)</f>
         <v/>
       </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>VOA 2026 list. A sports-use revaluation may lower it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Rates multiplier 2026/27</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="C91" s="17" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D91" s="17" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E91" s="18">
+        <f>CHOOSE($C$2,B91,C91,D91)</f>
+        <v/>
+      </c>
+      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Other operating costs</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Rates relief % override (blank = use structure)</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="n"/>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="9" t="n"/>
+      <c r="E92" s="19" t="n"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>TVBC can grant a local non-profit up to 100% at its discretion</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Café cost of sales (1 − gross margin)</t>
-        </is>
-      </c>
-      <c r="B93" s="20">
-        <f>1-B49</f>
-        <v/>
-      </c>
-      <c r="C93" s="20">
-        <f>1-C49</f>
-        <v/>
-      </c>
-      <c r="D93" s="20">
-        <f>1-D49</f>
-        <v/>
-      </c>
-      <c r="E93" s="10">
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C93" s="11" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D93" s="11" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E93" s="12">
         <f>CHOOSE($C$2,B93,C93,D93)</f>
         <v/>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Derived from café gross margin</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Booking, payments, software as % of income</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C94" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D94" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E94" s="10">
+          <t>Repairs and maintenance sinking fund (FRI)</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C94" s="11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E94" s="12">
         <f>CHOOSE($C$2,B94,C94,D94)</f>
         <v/>
       </c>
@@ -2163,17 +2147,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Utilities gross</t>
         </is>
       </c>
       <c r="B95" s="11" t="n">
-        <v>30000</v>
+        <v>90000</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>35000</v>
+        <v>70000</v>
       </c>
       <c r="E95" s="12">
         <f>CHOOSE($C$2,B95,C95,D95)</f>
@@ -2184,17 +2168,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Accountancy, legal, audit</t>
+          <t>Benefit of the 438 kWp roof PV (if the tenant gets the power)</t>
         </is>
       </c>
       <c r="B96" s="11" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="E96" s="12">
         <f>CHOOSE($C$2,B96,C96,D96)</f>
@@ -2202,76 +2186,76 @@
       </c>
       <c r="F96" t="inlineStr"/>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Equipment and consumables</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C97" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D97" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E97" s="12">
-        <f>CHOOSE($C$2,B97,C97,D97)</f>
-        <v/>
-      </c>
-      <c r="F97" t="inlineStr"/>
-    </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Contingency on controllable costs</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C98" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D98" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E98" s="10">
-        <f>CHOOSE($C$2,B98,C98,D98)</f>
-        <v/>
-      </c>
-      <c r="F98" t="inlineStr"/>
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Staff (salaries; on-costs added below)</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>General manager</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E99" s="12">
+        <f>CHOOSE($C$2,B99,C99,D99)</f>
+        <v/>
+      </c>
+      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Ramp (share of steady-state income)</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6" t="n"/>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="6" t="n"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Duty managers (count)</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" s="8">
+        <f>CHOOSE($C$2,B100,C100,D100)</f>
+        <v/>
+      </c>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="B101" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C101" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D101" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E101" s="10">
+          <t>Duty manager salary</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C101" s="11" t="n">
+        <v>28000</v>
+      </c>
+      <c r="D101" s="11" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E101" s="12">
         <f>CHOOSE($C$2,B101,C101,D101)</f>
         <v/>
       </c>
@@ -2280,19 +2264,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C102" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D102" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E102" s="10">
+          <t>Reception and café staff (FTE)</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E102" s="8">
         <f>CHOOSE($C$2,B102,C102,D102)</f>
         <v/>
       </c>
@@ -2301,19 +2285,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C103" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E103" s="10">
+          <t>Reception / café salary</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C103" s="11" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D103" s="11" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E103" s="12">
         <f>CHOOSE($C$2,B103,C103,D103)</f>
         <v/>
       </c>
@@ -2322,19 +2306,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C104" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="D104" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E104" s="10">
+          <t>Cleaners (FTE)</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" s="8">
         <f>CHOOSE($C$2,B104,C104,D104)</f>
         <v/>
       </c>
@@ -2343,81 +2327,406 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B105" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="D105" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E105" s="10">
+          <t>Cleaner salary</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C105" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D105" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E105" s="12">
         <f>CHOOSE($C$2,B105,C105,D105)</f>
         <v/>
       </c>
       <c r="F105" t="inlineStr"/>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Marketing and community officer</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C106" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E106" s="12">
+        <f>CHOOSE($C$2,B106,C106,D106)</f>
+        <v/>
+      </c>
+      <c r="F106" t="inlineStr"/>
+    </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Capital and finance</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="n"/>
-      <c r="C107" s="6" t="n"/>
-      <c r="D107" s="6" t="n"/>
-      <c r="E107" s="6" t="n"/>
-      <c r="F107" s="6" t="n"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Coaching cost as % of Momentum programme + S&amp;C income</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E107" s="10">
+        <f>CHOOSE($C$2,B107,C107,D107)</f>
+        <v/>
+      </c>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Loan interest rate</t>
+          <t>Employer on-costs (NI, pension)</t>
         </is>
       </c>
       <c r="B108" s="9" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="E108" s="10">
         <f>CHOOSE($C$2,B108,C108,D108)</f>
         <v/>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Other operating costs</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="n"/>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="6" t="n"/>
+      <c r="E110" s="6" t="n"/>
+      <c r="F110" s="6" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Café cost of sales (1 − gross margin)</t>
+        </is>
+      </c>
+      <c r="B111" s="20">
+        <f>1-B67</f>
+        <v/>
+      </c>
+      <c r="C111" s="20">
+        <f>1-C67</f>
+        <v/>
+      </c>
+      <c r="D111" s="20">
+        <f>1-D67</f>
+        <v/>
+      </c>
+      <c r="E111" s="10">
+        <f>CHOOSE($C$2,B111,C111,D111)</f>
+        <v/>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Derived from café gross margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Booking, payments, software as % of income</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E112" s="10">
+        <f>CHOOSE($C$2,B112,C112,D112)</f>
+        <v/>
+      </c>
+      <c r="F112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C113" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D113" s="11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E113" s="12">
+        <f>CHOOSE($C$2,B113,C113,D113)</f>
+        <v/>
+      </c>
+      <c r="F113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Accountancy, legal, audit</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E114" s="12">
+        <f>CHOOSE($C$2,B114,C114,D114)</f>
+        <v/>
+      </c>
+      <c r="F114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Equipment and consumables</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D115" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E115" s="12">
+        <f>CHOOSE($C$2,B115,C115,D115)</f>
+        <v/>
+      </c>
+      <c r="F115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Contingency on controllable costs</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E116" s="10">
+        <f>CHOOSE($C$2,B116,C116,D116)</f>
+        <v/>
+      </c>
+      <c r="F116" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Ramp (share of steady-state income)</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="6" t="n"/>
+      <c r="E118" s="6" t="n"/>
+      <c r="F118" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C119" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E119" s="10">
+        <f>CHOOSE($C$2,B119,C119,D119)</f>
+        <v/>
+      </c>
+      <c r="F119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E120" s="10">
+        <f>CHOOSE($C$2,B120,C120,D120)</f>
+        <v/>
+      </c>
+      <c r="F120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C121" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E121" s="10">
+        <f>CHOOSE($C$2,B121,C121,D121)</f>
+        <v/>
+      </c>
+      <c r="F121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C122" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E122" s="10">
+        <f>CHOOSE($C$2,B122,C122,D122)</f>
+        <v/>
+      </c>
+      <c r="F122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E123" s="10">
+        <f>CHOOSE($C$2,B123,C123,D123)</f>
+        <v/>
+      </c>
+      <c r="F123" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Capital and finance</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="n"/>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="6" t="n"/>
+      <c r="E125" s="6" t="n"/>
+      <c r="F125" s="6" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Loan interest rate</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C126" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E126" s="10">
+        <f>CHOOSE($C$2,B126,C126,D126)</f>
+        <v/>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Pitch Together 6%; LTA 5%; Charity Bank / Triodos similar</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>Loan term (years)</t>
         </is>
       </c>
-      <c r="B109" s="7" t="n">
+      <c r="B127" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C109" s="7" t="n">
+      <c r="C127" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D109" s="7" t="n">
+      <c r="D127" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E109" s="8">
-        <f>CHOOSE($C$2,B109,C109,D109)</f>
-        <v/>
-      </c>
-      <c r="F109" t="inlineStr"/>
+      <c r="E127" s="8">
+        <f>CHOOSE($C$2,B127,C127,D127)</f>
+        <v/>
+      </c>
+      <c r="F127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2785,7 +3094,7 @@
         </is>
       </c>
       <c r="B17" s="20">
-        <f>IF(ISNUMBER(Inputs!$E$74),Inputs!$E$74,INDEX($B$14:$E$14,1,Inputs!$C$3))</f>
+        <f>IF(ISNUMBER(Inputs!$E$92),Inputs!$E$92,INDEX($B$14:$E$14,1,Inputs!$C$3))</f>
         <v/>
       </c>
     </row>
@@ -2823,7 +3132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2870,7 +3179,7 @@
         </is>
       </c>
       <c r="B4" s="26">
-        <f>(Inputs!$E$7*Inputs!$E$13-Inputs!$E$14)*Inputs!$E$15*Inputs!$E$16*Inputs!$E$9</f>
+        <f>(Inputs!$E$7*Inputs!$E$16-Inputs!$E$17)*Inputs!$E$18*Inputs!$E$19*Inputs!$E$12</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
@@ -2886,7 +3195,7 @@
         </is>
       </c>
       <c r="B5" s="26">
-        <f>Inputs!$E$7*Inputs!$E$17*Inputs!$E$18*Inputs!$E$19*Inputs!$E$9</f>
+        <f>Inputs!$E$7*Inputs!$E$20*Inputs!$E$21*Inputs!$E$22*Inputs!$E$12</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -2898,7 +3207,7 @@
         </is>
       </c>
       <c r="B6" s="26">
-        <f>Inputs!$E$7*Inputs!$E$20*Inputs!$E$21*Inputs!$E$22*Inputs!$E$9</f>
+        <f>Inputs!$E$7*Inputs!$E$23*Inputs!$E$24*Inputs!$E$25*Inputs!$E$12</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -2910,7 +3219,7 @@
         </is>
       </c>
       <c r="B7" s="26">
-        <f>IF(Inputs!$E$25=1,Inputs!$E$26,Inputs!$E$14*Inputs!$E$16*(1-Inputs!$E$27)*Inputs!$E$28)</f>
+        <f>IF(Inputs!$E$28=1,Inputs!$E$29,Inputs!$E$17*Inputs!$E$19*(1-Inputs!$E$30)*Inputs!$E$31)</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
@@ -2926,7 +3235,7 @@
         </is>
       </c>
       <c r="B8" s="26">
-        <f>Inputs!$E$8*Inputs!$E$31*Inputs!$E$32*Inputs!$E$33*Inputs!$E$9</f>
+        <f>Inputs!$E$8*Inputs!$E$34*Inputs!$E$35*Inputs!$E$36*Inputs!$E$12</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -2934,11 +3243,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gym memberships</t>
+          <t>Pickleball court hire</t>
         </is>
       </c>
       <c r="B9" s="26">
-        <f>Inputs!$E$36*Inputs!$E$37*12</f>
+        <f>Inputs!$E$9*Inputs!$E$39*Inputs!$E$40*Inputs!$E$41*Inputs!$E$12</f>
         <v/>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -2946,11 +3255,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Netball S&amp;C and injury-prevention classes</t>
+          <t>Winter cricket nets</t>
         </is>
       </c>
       <c r="B10" s="26">
-        <f>Inputs!$E$38*Inputs!$E$39*Inputs!$E$40*Inputs!$E$9</f>
+        <f>Inputs!$E$10*Inputs!$E$45*Inputs!$E$46*Inputs!$E$47*Inputs!$E$44</f>
         <v/>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -2958,11 +3267,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Physio rooms and programmes</t>
+          <t>Bouldering room</t>
         </is>
       </c>
       <c r="B11" s="26">
-        <f>Inputs!$E$10*Inputs!$E$43*12+Inputs!$E$44</f>
+        <f>Inputs!$E$11*Inputs!$E$50</f>
         <v/>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -2970,11 +3279,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Café and bar sales</t>
+          <t>Gym memberships</t>
         </is>
       </c>
       <c r="B12" s="26">
-        <f>Inputs!$E$47*Inputs!$E$48*Inputs!$E$9</f>
+        <f>Inputs!$E$54*Inputs!$E$55*12</f>
         <v/>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -2982,11 +3291,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tournaments and events</t>
+          <t>Netball S&amp;C and injury-prevention classes</t>
         </is>
       </c>
       <c r="B13" s="26">
-        <f>Inputs!$E$52*Inputs!$E$53</f>
+        <f>Inputs!$E$56*Inputs!$E$57*Inputs!$E$58*Inputs!$E$12</f>
         <v/>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -2994,11 +3303,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Holiday camps (Mini Momentum)</t>
+          <t>Physio rooms and programmes</t>
         </is>
       </c>
       <c r="B14" s="26">
-        <f>Inputs!$E$54*Inputs!$E$55*Inputs!$E$56*5</f>
+        <f>Inputs!$E$13*Inputs!$E$61*12+Inputs!$E$62</f>
         <v/>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -3006,11 +3315,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Parties</t>
+          <t>Café and bar sales</t>
         </is>
       </c>
       <c r="B15" s="26">
-        <f>Inputs!$E$57*Inputs!$E$58*Inputs!$E$9</f>
+        <f>Inputs!$E$65*Inputs!$E$66*Inputs!$E$12</f>
         <v/>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -3018,11 +3327,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Meeting room hire</t>
+          <t>Tournaments and events</t>
         </is>
       </c>
       <c r="B16" s="26">
-        <f>Inputs!$E$59</f>
+        <f>Inputs!$E$70*Inputs!$E$71</f>
         <v/>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -3030,11 +3339,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sponsorship and naming</t>
+          <t>Holiday camps (Mini Momentum)</t>
         </is>
       </c>
       <c r="B17" s="26">
-        <f>Inputs!$E$62+Inputs!$E$63*Inputs!$E$64+Inputs!$E$65</f>
+        <f>Inputs!$E$72*Inputs!$E$73*Inputs!$E$74*5</f>
         <v/>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -3042,83 +3351,79 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Donations (+ Gift Aid if charity/CASC)</t>
+          <t>Parties</t>
         </is>
       </c>
       <c r="B18" s="26">
-        <f>Inputs!$E$66*(1+0.25*Structure!$B$18)</f>
+        <f>Inputs!$E$75*Inputs!$E$76*Inputs!$E$12</f>
         <v/>
       </c>
       <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>Total income</t>
-        </is>
-      </c>
-      <c r="B19" s="12">
-        <f>SUM(B4:B18)</f>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Meeting room hire</t>
+        </is>
+      </c>
+      <c r="B19" s="26">
+        <f>Inputs!$E$77</f>
         <v/>
       </c>
       <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sponsorship and naming</t>
+        </is>
+      </c>
+      <c r="B20" s="26">
+        <f>Inputs!$E$80+Inputs!$E$81*Inputs!$E$82+Inputs!$E$83</f>
+        <v/>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Donations (+ Gift Aid if charity/CASC)</t>
         </is>
       </c>
       <c r="B21" s="26">
-        <f>Inputs!$E$69</f>
+        <f>Inputs!$E$84*(1+0.25*Structure!$B$18)</f>
         <v/>
       </c>
       <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Business rates after relief</t>
-        </is>
-      </c>
-      <c r="B22" s="26">
-        <f>Inputs!$E$72*Inputs!$E$73*(1-Structure!$B$17)</f>
-        <v/>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>RV x multiplier x (1 − relief from Structure sheet)</t>
-        </is>
-      </c>
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B22" s="12">
+        <f>SUM(B4:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="B23" s="26">
-        <f>Inputs!$E$75</f>
-        <v/>
-      </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Repairs and maintenance (FRI)</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="B24" s="26">
-        <f>Inputs!$E$76</f>
+        <f>Inputs!$E$87</f>
         <v/>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -3126,87 +3431,95 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Utilities net of PV</t>
+          <t>Business rates after relief</t>
         </is>
       </c>
       <c r="B25" s="26">
-        <f>Inputs!$E$77-Inputs!$E$78</f>
-        <v/>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <f>Inputs!$E$90*Inputs!$E$91*(1-Structure!$B$17)</f>
+        <v/>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RV x multiplier x (1 − relief from Structure sheet)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Total occupancy</t>
-        </is>
-      </c>
-      <c r="B26" s="28">
-        <f>SUM(B21:B25)</f>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B26" s="26">
+        <f>Inputs!$E$93</f>
         <v/>
       </c>
       <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Repairs and maintenance (FRI)</t>
+        </is>
+      </c>
+      <c r="B27" s="26">
+        <f>Inputs!$E$94</f>
+        <v/>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Utilities net of PV</t>
+        </is>
+      </c>
+      <c r="B28" s="26">
+        <f>Inputs!$E$95-Inputs!$E$96</f>
+        <v/>
+      </c>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Total occupancy</t>
+        </is>
+      </c>
+      <c r="B29" s="28">
+        <f>SUM(B24:B28)</f>
+        <v/>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Salaried staff</t>
         </is>
       </c>
-      <c r="B28" s="26">
-        <f>(Inputs!$E$81+Inputs!$E$82*Inputs!$E$83+Inputs!$E$84*Inputs!$E$85+Inputs!$E$86*Inputs!$E$87+Inputs!$E$88)*(1+Inputs!$E$90)</f>
-        <v/>
-      </c>
-      <c r="C28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Coaches and S&amp;C (variable; programme coaching only in mode 1)</t>
-        </is>
-      </c>
-      <c r="B29" s="26">
-        <f>(IF(Inputs!$E$25=1,B7,0)+B10)*Inputs!$E$89*(1+Inputs!$E$90)</f>
-        <v/>
-      </c>
-      <c r="C29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Total staff</t>
-        </is>
-      </c>
-      <c r="B30" s="28">
-        <f>B28+B29</f>
-        <v/>
-      </c>
-      <c r="C30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Other operating</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
+      <c r="B31" s="26">
+        <f>(Inputs!$E$99+Inputs!$E$100*Inputs!$E$101+Inputs!$E$102*Inputs!$E$103+Inputs!$E$104*Inputs!$E$105+Inputs!$E$106)*(1+Inputs!$E$108)</f>
+        <v/>
+      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Café cost of sales</t>
+          <t>Coaches and S&amp;C (variable; programme coaching only in mode 1)</t>
         </is>
       </c>
       <c r="B32" s="26">
-        <f>B12*(1-Inputs!$E$49)</f>
+        <f>(IF(Inputs!$E$28=1,B7,0)+B13)*Inputs!$E$107*(1+Inputs!$E$108)</f>
         <v/>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -3214,47 +3527,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Booking, payments, software</t>
+          <t>Bouldering staff (only if the room exists)</t>
         </is>
       </c>
       <c r="B33" s="26">
-        <f>B19*Inputs!$E$94</f>
+        <f>IF(Inputs!$E$11&gt;0,Inputs!$E$51*(1+Inputs!$E$108),0)</f>
         <v/>
       </c>
       <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B34" s="26">
-        <f>Inputs!$E$95</f>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Total staff</t>
+        </is>
+      </c>
+      <c r="B34" s="28">
+        <f>B31+B32+B33</f>
         <v/>
       </c>
       <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="B35" s="26">
-        <f>Inputs!$E$96</f>
-        <v/>
-      </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Other operating</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Equipment and consumables</t>
+          <t>Café cost of sales</t>
         </is>
       </c>
       <c r="B36" s="26">
-        <f>Inputs!$E$97</f>
+        <f>B15*(1-Inputs!$E$67)</f>
         <v/>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -3262,110 +3571,158 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Booking, payments, software</t>
+        </is>
+      </c>
+      <c r="B37" s="26">
+        <f>B22*Inputs!$E$112</f>
+        <v/>
+      </c>
+      <c r="C37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B38" s="26">
+        <f>Inputs!$E$113</f>
+        <v/>
+      </c>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="B39" s="26">
+        <f>Inputs!$E$114</f>
+        <v/>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Equipment and consumables</t>
+        </is>
+      </c>
+      <c r="B40" s="26">
+        <f>Inputs!$E$115</f>
+        <v/>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="B37" s="26">
-        <f>(B23+B24+B25+B30+B32+B33+B34+B35+B36)*Inputs!$E$98</f>
-        <v/>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B41" s="26">
+        <f>(B26+B27+B28+B34+B36+B37+B38+B39+B40)*Inputs!$E$116</f>
+        <v/>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>on everything except rent and rates</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Total other operating</t>
         </is>
       </c>
-      <c r="B38" s="28">
-        <f>SUM(B32:B37)</f>
-        <v/>
-      </c>
-      <c r="C38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="B42" s="28">
+        <f>SUM(B36:B41)</f>
+        <v/>
+      </c>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="B43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Total costs</t>
         </is>
       </c>
-      <c r="B40" s="28">
-        <f>B26+B30+B38</f>
-        <v/>
-      </c>
-      <c r="C40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="27" t="inlineStr">
+      <c r="B44" s="28">
+        <f>B29+B34+B42</f>
+        <v/>
+      </c>
+      <c r="C44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>Surplus before loan repayments (EBITDA)</t>
         </is>
       </c>
-      <c r="B41" s="12">
-        <f>B19-B40</f>
-        <v/>
-      </c>
-      <c r="C41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="B45" s="12">
+        <f>B22-B44</f>
+        <v/>
+      </c>
+      <c r="C45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Loan repayments (from Capital sheet)</t>
         </is>
       </c>
-      <c r="B42" s="26">
+      <c r="B46" s="26">
         <f>-Capital!$B$40</f>
         <v/>
       </c>
-      <c r="C42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="27" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>Surplus after loan repayments</t>
         </is>
       </c>
-      <c r="B43" s="12">
-        <f>B41+B42</f>
-        <v/>
-      </c>
-      <c r="C43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="B47" s="12">
+        <f>B45+B46</f>
+        <v/>
+      </c>
+      <c r="C47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Memo: rates with no relief</t>
         </is>
       </c>
-      <c r="B44" s="26">
-        <f>Inputs!$E$72*Inputs!$E$73</f>
-        <v/>
-      </c>
-      <c r="C44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="B48" s="26">
+        <f>Inputs!$E$90*Inputs!$E$91</f>
+        <v/>
+      </c>
+      <c r="C48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Memo: rates saved by the structure</t>
         </is>
       </c>
-      <c r="B45" s="26">
-        <f>B44-B22</f>
-        <v/>
-      </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="B49" s="26">
+        <f>B48-B25</f>
+        <v/>
+      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3437,23 +3794,23 @@
         </is>
       </c>
       <c r="B3" s="26">
-        <f>('Steady state'!$B$19-'Steady state'!$B$17-'Steady state'!$B$18)*Inputs!$E$101+'Steady state'!$B$17+'Steady state'!$B$18</f>
+        <f>('Steady state'!$B$22-'Steady state'!$B$20-'Steady state'!$B$21)*Inputs!$E$119+'Steady state'!$B$20+'Steady state'!$B$21</f>
         <v/>
       </c>
       <c r="C3" s="26">
-        <f>('Steady state'!$B$19-'Steady state'!$B$17-'Steady state'!$B$18)*Inputs!$E$102+'Steady state'!$B$17+'Steady state'!$B$18</f>
+        <f>('Steady state'!$B$22-'Steady state'!$B$20-'Steady state'!$B$21)*Inputs!$E$120+'Steady state'!$B$20+'Steady state'!$B$21</f>
         <v/>
       </c>
       <c r="D3" s="26">
-        <f>('Steady state'!$B$19-'Steady state'!$B$17-'Steady state'!$B$18)*Inputs!$E$103+'Steady state'!$B$17+'Steady state'!$B$18</f>
+        <f>('Steady state'!$B$22-'Steady state'!$B$20-'Steady state'!$B$21)*Inputs!$E$121+'Steady state'!$B$20+'Steady state'!$B$21</f>
         <v/>
       </c>
       <c r="E3" s="26">
-        <f>('Steady state'!$B$19-'Steady state'!$B$17-'Steady state'!$B$18)*Inputs!$E$104+'Steady state'!$B$17+'Steady state'!$B$18</f>
+        <f>('Steady state'!$B$22-'Steady state'!$B$20-'Steady state'!$B$21)*Inputs!$E$122+'Steady state'!$B$20+'Steady state'!$B$21</f>
         <v/>
       </c>
       <c r="F3" s="26">
-        <f>('Steady state'!$B$19-'Steady state'!$B$17-'Steady state'!$B$18)*Inputs!$E$105+'Steady state'!$B$17+'Steady state'!$B$18</f>
+        <f>('Steady state'!$B$22-'Steady state'!$B$20-'Steady state'!$B$21)*Inputs!$E$123+'Steady state'!$B$20+'Steady state'!$B$21</f>
         <v/>
       </c>
       <c r="G3" s="28">
@@ -3468,23 +3825,23 @@
         </is>
       </c>
       <c r="B4" s="26">
-        <f>-'Steady state'!$B$21*(12-Inputs!$E$70)/12</f>
+        <f>-'Steady state'!$B$24*(12-Inputs!$E$88)/12</f>
         <v/>
       </c>
       <c r="C4" s="26">
-        <f>-'Steady state'!$B$21*Inputs!$E$71</f>
+        <f>-'Steady state'!$B$24*Inputs!$E$89</f>
         <v/>
       </c>
       <c r="D4" s="26">
-        <f>-'Steady state'!$B$21*1</f>
+        <f>-'Steady state'!$B$24*1</f>
         <v/>
       </c>
       <c r="E4" s="26">
-        <f>-'Steady state'!$B$21*1</f>
+        <f>-'Steady state'!$B$24*1</f>
         <v/>
       </c>
       <c r="F4" s="26">
-        <f>-'Steady state'!$B$21*1</f>
+        <f>-'Steady state'!$B$24*1</f>
         <v/>
       </c>
       <c r="G4" s="28">
@@ -3499,23 +3856,23 @@
         </is>
       </c>
       <c r="B5" s="26">
-        <f>-'Steady state'!$B$22</f>
+        <f>-'Steady state'!$B$25</f>
         <v/>
       </c>
       <c r="C5" s="26">
-        <f>-'Steady state'!$B$22</f>
+        <f>-'Steady state'!$B$25</f>
         <v/>
       </c>
       <c r="D5" s="26">
-        <f>-'Steady state'!$B$22</f>
+        <f>-'Steady state'!$B$25</f>
         <v/>
       </c>
       <c r="E5" s="26">
-        <f>-'Steady state'!$B$22</f>
+        <f>-'Steady state'!$B$25</f>
         <v/>
       </c>
       <c r="F5" s="26">
-        <f>-'Steady state'!$B$22</f>
+        <f>-'Steady state'!$B$25</f>
         <v/>
       </c>
       <c r="G5" s="28">
@@ -3530,23 +3887,23 @@
         </is>
       </c>
       <c r="B6" s="26">
-        <f>-('Steady state'!$B$23+'Steady state'!$B$24+'Steady state'!$B$25)</f>
+        <f>-('Steady state'!$B$26+'Steady state'!$B$27+'Steady state'!$B$28)</f>
         <v/>
       </c>
       <c r="C6" s="26">
-        <f>-('Steady state'!$B$23+'Steady state'!$B$24+'Steady state'!$B$25)</f>
+        <f>-('Steady state'!$B$26+'Steady state'!$B$27+'Steady state'!$B$28)</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>-('Steady state'!$B$23+'Steady state'!$B$24+'Steady state'!$B$25)</f>
+        <f>-('Steady state'!$B$26+'Steady state'!$B$27+'Steady state'!$B$28)</f>
         <v/>
       </c>
       <c r="E6" s="26">
-        <f>-('Steady state'!$B$23+'Steady state'!$B$24+'Steady state'!$B$25)</f>
+        <f>-('Steady state'!$B$26+'Steady state'!$B$27+'Steady state'!$B$28)</f>
         <v/>
       </c>
       <c r="F6" s="26">
-        <f>-('Steady state'!$B$23+'Steady state'!$B$24+'Steady state'!$B$25)</f>
+        <f>-('Steady state'!$B$26+'Steady state'!$B$27+'Steady state'!$B$28)</f>
         <v/>
       </c>
       <c r="G6" s="28">
@@ -3561,23 +3918,23 @@
         </is>
       </c>
       <c r="B7" s="26">
-        <f>-'Steady state'!$B$28*0.85</f>
+        <f>-'Steady state'!$B$31*0.85</f>
         <v/>
       </c>
       <c r="C7" s="26">
-        <f>-'Steady state'!$B$28*1</f>
+        <f>-'Steady state'!$B$31*1</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>-'Steady state'!$B$28*1</f>
+        <f>-'Steady state'!$B$31*1</f>
         <v/>
       </c>
       <c r="E7" s="26">
-        <f>-'Steady state'!$B$28*1</f>
+        <f>-'Steady state'!$B$31*1</f>
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>-'Steady state'!$B$28*1</f>
+        <f>-'Steady state'!$B$31*1</f>
         <v/>
       </c>
       <c r="G7" s="28">
@@ -3592,23 +3949,23 @@
         </is>
       </c>
       <c r="B8" s="26">
-        <f>-'Steady state'!$B$29*Inputs!$E$101</f>
+        <f>-'Steady state'!$B$32*Inputs!$E$119</f>
         <v/>
       </c>
       <c r="C8" s="26">
-        <f>-'Steady state'!$B$29*Inputs!$E$102</f>
+        <f>-'Steady state'!$B$32*Inputs!$E$120</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>-'Steady state'!$B$29*Inputs!$E$103</f>
+        <f>-'Steady state'!$B$32*Inputs!$E$121</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>-'Steady state'!$B$29*Inputs!$E$104</f>
+        <f>-'Steady state'!$B$32*Inputs!$E$122</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>-'Steady state'!$B$29*Inputs!$E$105</f>
+        <f>-'Steady state'!$B$32*Inputs!$E$123</f>
         <v/>
       </c>
       <c r="G8" s="28">
@@ -3623,23 +3980,23 @@
         </is>
       </c>
       <c r="B9" s="26">
-        <f>-'Steady state'!$B$32*Inputs!$E$101</f>
+        <f>-'Steady state'!$B$36*Inputs!$E$119</f>
         <v/>
       </c>
       <c r="C9" s="26">
-        <f>-'Steady state'!$B$32*Inputs!$E$102</f>
+        <f>-'Steady state'!$B$36*Inputs!$E$120</f>
         <v/>
       </c>
       <c r="D9" s="26">
-        <f>-'Steady state'!$B$32*Inputs!$E$103</f>
+        <f>-'Steady state'!$B$36*Inputs!$E$121</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>-'Steady state'!$B$32*Inputs!$E$104</f>
+        <f>-'Steady state'!$B$36*Inputs!$E$122</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>-'Steady state'!$B$32*Inputs!$E$105</f>
+        <f>-'Steady state'!$B$36*Inputs!$E$123</f>
         <v/>
       </c>
       <c r="G9" s="28">
@@ -3654,23 +4011,23 @@
         </is>
       </c>
       <c r="B10" s="26">
-        <f>-'Steady state'!$B$33*Inputs!$E$101</f>
+        <f>-'Steady state'!$B$37*Inputs!$E$119</f>
         <v/>
       </c>
       <c r="C10" s="26">
-        <f>-'Steady state'!$B$33*Inputs!$E$102</f>
+        <f>-'Steady state'!$B$37*Inputs!$E$120</f>
         <v/>
       </c>
       <c r="D10" s="26">
-        <f>-'Steady state'!$B$33*Inputs!$E$103</f>
+        <f>-'Steady state'!$B$37*Inputs!$E$121</f>
         <v/>
       </c>
       <c r="E10" s="26">
-        <f>-'Steady state'!$B$33*Inputs!$E$104</f>
+        <f>-'Steady state'!$B$37*Inputs!$E$122</f>
         <v/>
       </c>
       <c r="F10" s="26">
-        <f>-'Steady state'!$B$33*Inputs!$E$105</f>
+        <f>-'Steady state'!$B$37*Inputs!$E$123</f>
         <v/>
       </c>
       <c r="G10" s="28">
@@ -3685,23 +4042,23 @@
         </is>
       </c>
       <c r="B11" s="26">
-        <f>-('Steady state'!$B$34*1.5+'Steady state'!$B$35+'Steady state'!$B$36)</f>
+        <f>-('Steady state'!$B$38*1.5+'Steady state'!$B$39+'Steady state'!$B$40)</f>
         <v/>
       </c>
       <c r="C11" s="26">
-        <f>-('Steady state'!$B$34*1+'Steady state'!$B$35+'Steady state'!$B$36)</f>
+        <f>-('Steady state'!$B$38*1+'Steady state'!$B$39+'Steady state'!$B$40)</f>
         <v/>
       </c>
       <c r="D11" s="26">
-        <f>-('Steady state'!$B$34*1+'Steady state'!$B$35+'Steady state'!$B$36)</f>
+        <f>-('Steady state'!$B$38*1+'Steady state'!$B$39+'Steady state'!$B$40)</f>
         <v/>
       </c>
       <c r="E11" s="26">
-        <f>-('Steady state'!$B$34*1+'Steady state'!$B$35+'Steady state'!$B$36)</f>
+        <f>-('Steady state'!$B$38*1+'Steady state'!$B$39+'Steady state'!$B$40)</f>
         <v/>
       </c>
       <c r="F11" s="26">
-        <f>-('Steady state'!$B$34*1+'Steady state'!$B$35+'Steady state'!$B$36)</f>
+        <f>-('Steady state'!$B$38*1+'Steady state'!$B$39+'Steady state'!$B$40)</f>
         <v/>
       </c>
       <c r="G11" s="28">
@@ -3716,23 +4073,23 @@
         </is>
       </c>
       <c r="B12" s="26">
-        <f>-'Steady state'!$B$37*Inputs!$E$101</f>
+        <f>-'Steady state'!$B$41*Inputs!$E$119</f>
         <v/>
       </c>
       <c r="C12" s="26">
-        <f>-'Steady state'!$B$37*Inputs!$E$102</f>
+        <f>-'Steady state'!$B$41*Inputs!$E$120</f>
         <v/>
       </c>
       <c r="D12" s="26">
-        <f>-'Steady state'!$B$37*Inputs!$E$103</f>
+        <f>-'Steady state'!$B$41*Inputs!$E$121</f>
         <v/>
       </c>
       <c r="E12" s="26">
-        <f>-'Steady state'!$B$37*Inputs!$E$104</f>
+        <f>-'Steady state'!$B$41*Inputs!$E$122</f>
         <v/>
       </c>
       <c r="F12" s="26">
-        <f>-'Steady state'!$B$37*Inputs!$E$105</f>
+        <f>-'Steady state'!$B$41*Inputs!$E$123</f>
         <v/>
       </c>
       <c r="G12" s="28">
@@ -3929,11 +4286,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sports floor, 4 netball courts (~2,450 sq m at £110/sq m)</t>
+          <t>Sports floor, netball courts (630 sq m each at £110/sq m)</t>
         </is>
       </c>
       <c r="B3" s="26">
-        <f>Inputs!$E$7*612*110</f>
+        <f>Inputs!$E$7*630*110</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
@@ -3961,66 +4318,71 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gym fit-out and equipment (300 sq m)</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>120000</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Pickleball courts, cricket nets, bouldering room</t>
+        </is>
+      </c>
+      <c r="B5" s="26">
+        <f>Inputs!$E$9*8000+Inputs!$E$10*4000+Inputs!$E$11*700</f>
+        <v/>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£8k per pickleball court on the sports floor; £4k per retractable lane; £700/sq m bouldering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Heating and ventilation for occupied sport</t>
+          <t>Gym fit-out and equipment (~210 sq m in the span A end)</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Changing rooms, café, reception, partitions</t>
+          <t>Heating and ventilation for occupied sport</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Existing WCs and showers reduce this</t>
-        </is>
-      </c>
+        <v>150000</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Netball posts, nets, curtains, lighting changes, scoreboards</t>
+          <t>Changing rooms, café, reception, partitions</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>60000</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>300000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Existing WCs and showers reduce this</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Physio rooms and office conversion</t>
+          <t>Netball posts, nets, curtains, lighting changes, scoreboards</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT, booking system, access control, AV</t>
+          <t>Physio rooms and office conversion</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
@@ -4031,23 +4393,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Planning, design and professional fees (12%)</t>
-        </is>
-      </c>
-      <c r="B11" s="26">
-        <f>SUM(B3:B10)*0.12</f>
-        <v/>
+          <t>IT, booking system, access control, AV</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>40000</v>
       </c>
       <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Contingency (10%)</t>
+          <t>Planning, design and professional fees (12%)</t>
         </is>
       </c>
       <c r="B12" s="26">
-        <f>SUM(B3:B11)*0.10</f>
+        <f>SUM(B3:B11)*0.12</f>
         <v/>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -4055,91 +4416,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rent deposit or guarantee (6 months)</t>
+          <t>Contingency (10%)</t>
         </is>
       </c>
       <c r="B13" s="26">
-        <f>Inputs!$E$69/2</f>
-        <v/>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Negotiate a guarantee instead of cash</t>
-        </is>
-      </c>
+        <f>SUM(B3:B12)*0.10</f>
+        <v/>
+      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Rent deposit or guarantee (6 months)</t>
+        </is>
+      </c>
+      <c r="B14" s="26">
+        <f>Inputs!$E$87/2</f>
+        <v/>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Negotiate a guarantee instead of cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Working capital for years 1–2 (from 5 year sheet, + £50k buffer)</t>
         </is>
       </c>
-      <c r="B14" s="26">
+      <c r="B15" s="26">
         <f>MAX(0,-'5 year'!$B$20)+50000</f>
         <v/>
       </c>
-      <c r="C14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Total capital need</t>
         </is>
       </c>
-      <c r="B15" s="12">
-        <f>SUM(B3:B14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="B16" s="12">
+        <f>SUM(B3:B15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Sources (targets, not commitments)</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>£</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Route and status</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Landlord capital contribution</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ask: unit empty since 2023; they refurbished at cost</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>grant/equity</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Football Foundation multi-sport grassroots facilities</t>
+          <t>Landlord capital contribution</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netball named as a beneficiary of the £98m/yr programme; apply via Hampshire FA / England Netball</t>
+          <t>Ask: unit empty since 2023; they refurbished at cost</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4151,15 +4504,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>National Lottery Community Fund — Reaching Communities</t>
+          <t>Football Foundation multi-sport grassroots facilities</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£20k to £500k+; funds building work for CICs and charities</t>
+          <t>Netball named as a beneficiary of the £98m/yr programme; apply via Hampshire FA / England Netball</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4171,15 +4524,15 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Test Valley BC — S106 / CIL sport contributions</t>
+          <t>National Lottery Community Fund — Reaching Communities</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>East Anton and Picket Twenty growth; strategy forecasts a 6–8 court hall need by 2036</t>
+          <t>£20k to £500k+; funds building work for CICs and charities</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4191,15 +4544,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>England Netball / Sport England</t>
+          <t>Test Valley BC — S106 / CIL sport contributions</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Via the Netball Development Officer; EN has £21.2m from Sport England to 2029</t>
+          <t>East Anton and Picket Twenty growth; strategy forecasts a 6–8 court hall need by 2036</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4211,15 +4564,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Armed Forces Covenant Fund Trust</t>
+          <t>England Netball / Sport England</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Army HQ is in Andover; family and wellbeing programmes</t>
+          <t>Via the Netball Development Officer; EN has £21.2m from Sport England to 2029</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4231,15 +4584,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Charitable trusts (Garfield Weston, Bernard Sunley, Wolfson)</t>
+          <t>Armed Forces Covenant Fund Trust</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charity only</t>
+          <t>Army HQ is in Andover; family and wellbeing programmes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4251,15 +4604,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Founders, community investors, Crowdfunder</t>
+          <t>Charitable trusts (Garfield Weston, Bernard Sunley, Wolfson)</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Crowdfunder + Sport England match up to £15k; CIC ltd by shares for investors</t>
+          <t>Charity only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4271,15 +4624,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Donations, naming-rights advance</t>
+          <t>Founders, community investors, Crowdfunder</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Year-0 sponsorship paid up front</t>
+          <t>Crowdfunder + Sport England match up to £15k; CIC ltd by shares for investors</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4291,95 +4644,115 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LTA padel loan (Quick Access / Facility Loan)</t>
+          <t>Donations, naming-rights advance</t>
         </is>
       </c>
       <c r="B27" s="11" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>£25k–£250k at 5%, up to 10 years</t>
+          <t>Year-0 sponsorship paid up front</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>loan</t>
+          <t>grant/equity</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>LTA padel loan (Quick Access / Facility Loan)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£25k–£250k at 5%, up to 10 years</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>loan</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Charity Bank / Triodos / Pitch Together loan</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B29" s="11" t="n">
         <v>400000</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Pitch Together £25k–£300k at 6%; Charity Bank larger</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>loan</t>
         </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Total grants, donations and equity</t>
-        </is>
-      </c>
-      <c r="B30" s="26">
-        <f>SUMIF(D18:D28,"grant/equity",B18:B28)</f>
-        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Total loans</t>
+          <t>Total grants, donations and equity</t>
         </is>
       </c>
       <c r="B31" s="26">
-        <f>SUMIF(D18:D28,"loan",B18:B28)</f>
+        <f>SUMIF(D19:D29,"grant/equity",B19:B29)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Total sources</t>
-        </is>
-      </c>
-      <c r="B32" s="29">
-        <f>B30+B31</f>
+          <t>Total loans</t>
+        </is>
+      </c>
+      <c r="B32" s="26">
+        <f>SUMIF(D19:D29,"loan",B19:B29)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>Total sources</t>
+        </is>
+      </c>
+      <c r="B33" s="29">
+        <f>B31+B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>Surplus / (gap)</t>
         </is>
       </c>
-      <c r="B33" s="29">
-        <f>B32-B15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="B34" s="29">
+        <f>B33-B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Grants and donations as % of capital</t>
         </is>
       </c>
-      <c r="B35" s="30">
-        <f>B30/B15</f>
+      <c r="B36" s="30">
+        <f>B31/B16</f>
         <v/>
       </c>
     </row>
@@ -4397,7 +4770,7 @@
         </is>
       </c>
       <c r="B39" s="26">
-        <f>B31</f>
+        <f>B32</f>
         <v/>
       </c>
     </row>
@@ -4408,7 +4781,7 @@
         </is>
       </c>
       <c r="B40" s="12">
-        <f>IF(B39=0,0,-PMT(Inputs!$E$108,Inputs!$E$109,B39))</f>
+        <f>IF(B39=0,0,-PMT(Inputs!$E$126,Inputs!$E$127,B39))</f>
         <v/>
       </c>
     </row>
@@ -4475,11 +4848,11 @@
         <v>20</v>
       </c>
       <c r="C6" s="7">
-        <f>Inputs!$E$14</f>
+        <f>Inputs!$E$17</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>Inputs!$E$14</f>
+        <f>Inputs!$E$17</f>
         <v/>
       </c>
     </row>
@@ -4493,11 +4866,11 @@
         <v>30</v>
       </c>
       <c r="C7" s="7">
-        <f>Inputs!$E$28</f>
+        <f>Inputs!$E$31</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>Inputs!$E$28</f>
+        <f>Inputs!$E$31</f>
         <v/>
       </c>
     </row>
@@ -4511,11 +4884,11 @@
         <v>24</v>
       </c>
       <c r="C8" s="13">
-        <f>Inputs!$E$16*(1-Inputs!$E$27)</f>
+        <f>Inputs!$E$19*(1-Inputs!$E$30)</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>Inputs!$E$16*(1-Inputs!$E$27)</f>
+        <f>Inputs!$E$19*(1-Inputs!$E$30)</f>
         <v/>
       </c>
     </row>
@@ -4715,7 +5088,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Spaces, from the Hollis as-built survey (TVBC 23/02973/FULLN, drawing 10250 C10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Clear size</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Base use</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Alternatives that fit</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Span A (west), x 13.5–34 m</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>20 m x 52.5 m</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Court 1 + gym (18 x 20 m end)</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Court + 2 pickleball; court + walking netball</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>18.25 m court fits a 20 m span with 0.9 m each side</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Span B, x 34–54 m</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>20 m x 52.5 m</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Court 2 + 2 pickleball (end)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Court + gym; court + S&amp;C studio</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Same span; end zone 18 x 20 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Span C incl. extension, x 54–75 m</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>21 m x 60.5 m</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Court 3 + 2 padel (21 x 22 m leftover)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>Court 3 + bouldering room (~460 sq m); court 3 + 4 cricket lanes year-round</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Only 21 m spans take a 20 m padel court</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>East block, x 75–96 m</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>21 m x 33.5 m</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>3 padel</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Court 4 at league run-offs (33.5 m); 6 pickleball; futsal / small-sided</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Depends on the 75 m line: columns or beam</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Office block, ground</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>x 62–96 m, 4 m deep + SE corner</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Café, reception, changing (existing WCs and showers)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Office block, first floor</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>3,467 sq ft total offices</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>Physio rooms, meeting rooms, admin</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Sublet a suite</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>Air-conditioned, refurbished</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>All netball courts, Jan–Apr weekdays</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>4 lanes per court</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>Retractable cricket nets</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>Archery, indoor athletics hire</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Fills the dead daytime without capex on new space</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Height: eaves and valleys 7.1 m at every column row, each span has its own ridge (about 8.1 m at a 6° pitch). Momentum's leagues play in 6.7 m school halls today; England Netball's 7.5 m is for affiliated competition venues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>What was rejected and why: trampoline park and soft play (different operating model, insurance, staff-heavy); 5-a-side (competes with our own evening slots and with Goals/PowerLeague economics); esports and nursery (not sport, not us).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A13:E14"/>
+    <mergeCell ref="A16:E17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -4781,7 +5410,7 @@
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>What the model says: at Base, as a CIC with no rates relief, the venue roughly breaks even at steady state before loan repayments and loses money in years 1–2. Charity status or TVBC discretionary relief is worth about £154k a year, more than any single income line. Padel and the café carry the daytime.</t>
+          <t>Layout is 3 netball + 5 padel + 2 pickleball + winter cricket nets by default (Layout sheet). Set boulder_sqm to ~460 and padel to 3 to test a bouldering room instead of the two padel courts south of Court 3.</t>
         </is>
       </c>
     </row>
@@ -4791,7 +5420,7 @@
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>Biggest unknowns, in order: clear height under the roof; ground-lease user clause and planning; landlord incentives; padel fill; whether the tenant gets the PV electricity; VAT on rent and on fit-out (a VAT-exempt sports body cannot recover it — take advice).</t>
+          <t>What the model says: at Base, as a CIC with no rates relief, the venue roughly breaks even at steady state before loan repayments and loses money in years 1–2. Charity status or TVBC discretionary relief is worth about £154k a year, more than any single income line. Padel and the café carry the daytime.</t>
         </is>
       </c>
     </row>
@@ -4800,6 +5429,16 @@
     </row>
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Biggest unknowns, in order: clear height under the roof; ground-lease user clause and planning; landlord incentives; padel fill; whether the tenant gets the PV electricity; VAT on rent and on fit-out (a VAT-exempt sports body cannot recover it — take advice).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Grant figures are targets from published programme ranges: Football Foundation multi-sport (£98m/yr UK, netball named); Lottery Reaching Communities (£20k–£500k typical); LTA loans £25k–£250k at 5%; Pitch Together £25k–£300k at 6%; TVBC discretionary relief up to 100% for local non-profit recreation bodies (policy v2026.1).</t>
         </is>

--- a/docs/venue-model-andover-unit-28.xlsx
+++ b/docs/venue-model-andover-unit-28.xlsx
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="B46" s="26">
-        <f>-Capital!$B$40</f>
+        <f>-Capital!$B$43</f>
         <v/>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -4135,23 +4135,23 @@
         </is>
       </c>
       <c r="B14" s="26">
-        <f>-Capital!$B$40</f>
+        <f>-Capital!$B$43</f>
         <v/>
       </c>
       <c r="C14" s="26">
-        <f>-Capital!$B$40</f>
+        <f>-Capital!$B$43</f>
         <v/>
       </c>
       <c r="D14" s="26">
-        <f>-Capital!$B$40</f>
+        <f>-Capital!$B$43</f>
         <v/>
       </c>
       <c r="E14" s="26">
-        <f>-Capital!$B$40</f>
+        <f>-Capital!$B$43</f>
         <v/>
       </c>
       <c r="F14" s="26">
-        <f>-Capital!$B$40</f>
+        <f>-Capital!$B$43</f>
         <v/>
       </c>
       <c r="G14" s="28">
@@ -4250,7 +4250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4624,15 +4624,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Founders, community investors, Crowdfunder</t>
+          <t>Local sports charity: seed for Phase 1 and match funding</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>150000</v>
+        <v>25000</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Crowdfunder + Sport England match up to £15k; CIC ltd by shares for investors</t>
+          <t>Known to Adam; pays the survey, pre-app and engineer so no director funds Phase 1 personally</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4644,15 +4644,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Donations, naming-rights advance</t>
+          <t>Local private investors introduced by the charity (patient capital)</t>
         </is>
       </c>
       <c r="B27" s="11" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Year-0 sponsorship paid up front</t>
+          <t>Capped-dividend shares in a CIC ltd by shares, a rent-deposit guarantee, or donations via the charitable arm. If it comes as a 6% loan instead, add about £34k a year of service</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4664,124 +4664,164 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LTA padel loan (Quick Access / Facility Loan)</t>
+          <t>Crowdfunder with Sport England match</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>200000</v>
+        <v>30000</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£25k–£250k at 5%, up to 10 years</t>
+          <t>Match up to £15k; also a demand test</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>loan</t>
+          <t>grant/equity</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Donations, naming-rights advance</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Year-0 sponsorship paid up front</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>grant/equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LTA padel loan (Quick Access / Facility Loan)</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£25k–£250k at 5%, up to 10 years</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>loan</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Charity Bank / Triodos / Pitch Together loan</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B31" s="11" t="n">
         <v>400000</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Pitch Together £25k–£300k at 6%; Charity Bank larger</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>loan</t>
         </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Total grants, donations and equity</t>
-        </is>
-      </c>
-      <c r="B31" s="26">
-        <f>SUMIF(D19:D29,"grant/equity",B19:B29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Total loans</t>
-        </is>
-      </c>
-      <c r="B32" s="26">
-        <f>SUMIF(D19:D29,"loan",B19:B29)</f>
-        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Total sources</t>
-        </is>
-      </c>
-      <c r="B33" s="29">
-        <f>B31+B32</f>
+          <t>Total grants, donations and equity</t>
+        </is>
+      </c>
+      <c r="B33" s="26">
+        <f>SUMIF(D19:D31,"grant/equity",B19:B31)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>Total loans</t>
+        </is>
+      </c>
+      <c r="B34" s="26">
+        <f>SUMIF(D19:D31,"loan",B19:B31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Total sources</t>
+        </is>
+      </c>
+      <c r="B35" s="29">
+        <f>B33+B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
           <t>Surplus / (gap)</t>
         </is>
       </c>
-      <c r="B34" s="29">
-        <f>B33-B16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="B36" s="29">
+        <f>B35-B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Grants and donations as % of capital</t>
         </is>
       </c>
-      <c r="B36" s="30">
-        <f>B31/B16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="B38" s="30">
+        <f>B33/B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Loan service</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Loan principal</t>
         </is>
       </c>
-      <c r="B39" s="26">
-        <f>B32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="B42" s="26">
+        <f>B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Annual repayment (annuity)</t>
         </is>
       </c>
-      <c r="B40" s="12">
-        <f>IF(B39=0,0,-PMT(Inputs!$E$126,Inputs!$E$127,B39))</f>
+      <c r="B43" s="12">
+        <f>IF(B42=0,0,-PMT(Inputs!$E$126,Inputs!$E$127,B42))</f>
         <v/>
       </c>
     </row>

--- a/docs/venue-model-andover-unit-28.xlsx
+++ b/docs/venue-model-andover-unit-28.xlsx
@@ -82,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,7 +122,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4836,7 +4839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -4855,7 +4858,7 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Today, school halls cost Momentum about £24 per court-hour. The CIC must charge an arm's-length rate, so Momentum's league margin changes. This sheet shows what has to move.</t>
+          <t>School halls cost Momentum about £24 per court-hour. The CIC must charge an arm's-length rate. At £450 a season the league absorbs that easily; the venue's value to Momentum is room to grow past 24 teams in Andover, alongside new town leagues.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4867,7 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Today (Xero FY26)</t>
+          <t>Today (24 teams, £450, Xero FY26)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -4874,249 +4877,264 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>In the CIC, new fees</t>
+          <t>In the CIC, 36 teams at £480</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Evening court-hours per week</t>
+          <t>Teams in the Andover women's league</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7">
-        <f>Inputs!$E$17</f>
-        <v/>
-      </c>
-      <c r="D6" s="7">
-        <f>Inputs!$E$17</f>
-        <v/>
+        <v>24</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Weeks per year</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C7" s="7">
-        <f>Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="D7" s="7">
-        <f>Inputs!$E$31</f>
-        <v/>
+          <t>Fee per team per season</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="n">
+        <v>450</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>450</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rate per court-hour paid</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="C8" s="13">
-        <f>Inputs!$E$19*(1-Inputs!$E$30)</f>
-        <v/>
-      </c>
-      <c r="D8" s="13">
-        <f>Inputs!$E$19*(1-Inputs!$E$30)</f>
-        <v/>
+          <t>Seasons per year (each about 10 weeks)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Matches per court-hour</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>1.5</v>
+          <t>Matches per week (teams / 2)</t>
+        </is>
+      </c>
+      <c r="B9" s="32">
+        <f>B6/2</f>
+        <v/>
+      </c>
+      <c r="C9" s="32">
+        <f>C6/2</f>
+        <v/>
+      </c>
+      <c r="D9" s="32">
+        <f>D6/2</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fee per team per match</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>25</v>
+          <t>Matches per court-hour</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Other direct costs per match (umpires, insurance, prizes)</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>6</v>
+          <t>Court-hours per week (matches / matches per court-hour)</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>B9/B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="32">
+        <f>C9/C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="32">
+        <f>D9/D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Weeks per year (seasons x 10)</t>
+        </is>
+      </c>
+      <c r="B12" s="33">
+        <f>B8*10</f>
+        <v/>
+      </c>
+      <c r="C12" s="33">
+        <f>C8*10</f>
+        <v/>
+      </c>
+      <c r="D12" s="33">
+        <f>D8*10</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Matches per year</t>
-        </is>
-      </c>
-      <c r="B13" s="31">
-        <f>B6*B7*B9</f>
-        <v/>
-      </c>
-      <c r="C13" s="31">
-        <f>C6*C7*C9</f>
-        <v/>
-      </c>
-      <c r="D13" s="31">
-        <f>D6*D7*D9</f>
+          <t>Rate per court-hour paid</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="C13" s="34">
+        <f>Inputs!$E$19*(1-Inputs!$E$30)</f>
+        <v/>
+      </c>
+      <c r="D13" s="34">
+        <f>Inputs!$E$19*(1-Inputs!$E$30)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>League income (2 teams per match)</t>
-        </is>
-      </c>
-      <c r="B14" s="26">
-        <f>B13*2*B10</f>
-        <v/>
-      </c>
-      <c r="C14" s="26">
-        <f>C13*2*C10</f>
-        <v/>
-      </c>
-      <c r="D14" s="26">
-        <f>D13*2*D10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Court hire paid</t>
-        </is>
-      </c>
-      <c r="B15" s="26">
-        <f>-B6*B7*B8</f>
-        <v/>
-      </c>
-      <c r="C15" s="26">
-        <f>-C6*C7*C8</f>
-        <v/>
-      </c>
-      <c r="D15" s="26">
-        <f>-D6*D7*D8</f>
-        <v/>
+          <t>Other direct costs per match (umpires, insurance, prizes)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Other direct costs</t>
+          <t>League income (teams x fee x seasons)</t>
         </is>
       </c>
       <c r="B16" s="26">
-        <f>-B13*B11</f>
+        <f>B6*B7*B8</f>
         <v/>
       </c>
       <c r="C16" s="26">
-        <f>-C13*C11</f>
+        <f>C6*C7*C8</f>
         <v/>
       </c>
       <c r="D16" s="26">
-        <f>-D13*D11</f>
+        <f>D6*D7*D8</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>League gross profit</t>
-        </is>
-      </c>
-      <c r="B17" s="12">
-        <f>SUM(B14:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="12">
-        <f>SUM(C14:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="12">
-        <f>SUM(D14:D16)</f>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Court hire</t>
+        </is>
+      </c>
+      <c r="B17" s="26">
+        <f>-B11*B12*B13</f>
+        <v/>
+      </c>
+      <c r="C17" s="26">
+        <f>-C11*C12*C13</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>-D11*D12*D13</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B18" s="30">
-        <f>IF(B14=0,0,B17/B14)</f>
-        <v/>
-      </c>
-      <c r="C18" s="30">
-        <f>IF(C14=0,0,C17/C14)</f>
-        <v/>
-      </c>
-      <c r="D18" s="30">
-        <f>IF(D14=0,0,D17/D14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>Reference points: Xero FY26 league sales £43,781 and venue hire £14,647. Commercial leagues (Play Netball, Go Mammoth) charge £8–10 per player per match, about £56–70 per team. Momentum's £18 per team per match is the cheapest in the market by a distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+          <t>Other direct costs</t>
+        </is>
+      </c>
+      <c r="B18" s="26">
+        <f>-B9*B12*B14</f>
+        <v/>
+      </c>
+      <c r="C18" s="26">
+        <f>-C9*C12*C14</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>-D9*D12*D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>League gross profit</t>
+        </is>
+      </c>
+      <c r="B19" s="12">
+        <f>SUM(B16:B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="12">
+        <f>SUM(C16:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="12">
+        <f>SUM(D16:D18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Reference points: 24 teams x £450 x 4 ten-week seasons = £43,200 against Xero FY26 league sales of £43,781, i.e. £45 per team per match. Total venue hire £14,647 covers the league (about 8 court-hours a week) plus mixed, training, Netball Hour and pay-to-play. Commercial leagues charge £56–70 per team per match. Growth routes: more Andover divisions in the hub, and more towns (Basingstoke next) on the same model with the hub as home for finals, tournaments and training.</t>
+        </is>
+      </c>
+    </row>
     <row r="22"/>
-    <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+    <row r="23"/>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Governance: directors common to Momentum Ltd and the CIC must declare the conflict, the CIC board needs independent members, and the court-hire contract must be at the published rate. Funders and the CIC Regulator look for exactly this.</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26"/>
+    <row r="27"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:D3"/>
-    <mergeCell ref="A20:D22"/>
-    <mergeCell ref="A24:D26"/>
+    <mergeCell ref="A25:D27"/>
+    <mergeCell ref="A21:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5440,7 +5458,7 @@
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>Momentum Netball Ltd can stay independent and block-book courts from the CIC (mode 2 on Inputs). The Momentum Ltd sheet shows the effect on its league margin: at an arm's-length rate its £18 per team per match no longer covers the court, so fees rise or the league grows.</t>
+          <t>Momentum Netball Ltd can stay independent and block-book courts from the CIC (mode 2 on Inputs). The Momentum Ltd sheet shows the league at 24 teams x £450 x 4 ten-week seasons: the arm's-length court rate costs it about £5.4k a year; growth to 36 teams more than covers it.</t>
         </is>
       </c>
     </row>
